--- a/exports/trend_1d/UNITDSPR_full_report.xlsx
+++ b/exports/trend_1d/UNITDSPR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.52</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H2" t="n">
-        <v>711.42</v>
+        <v>683.25</v>
       </c>
       <c r="I2" t="n">
         <v>701.7747529543893</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>12.37</v>
       </c>
       <c r="L2" t="n">
         <v>0.64</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>14.23</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H3" t="n">
-        <v>745.3099999999999</v>
+        <v>757.85</v>
       </c>
       <c r="I3" t="n">
         <v>746.3578273828825</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.08</v>
+        <v>-10.92</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>12.61</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.97</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42177</v>
+        <v>42178</v>
       </c>
       <c r="H4" t="n">
-        <v>670.42</v>
+        <v>658.1799999999999</v>
       </c>
       <c r="I4" t="n">
         <v>668.0454562086817</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.54</v>
+        <v>-13.15</v>
       </c>
       <c r="L4" t="n">
-        <v>11.95</v>
+        <v>13.94</v>
       </c>
       <c r="M4" t="n">
         <v>2.55</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.82</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42201</v>
+        <v>42202</v>
       </c>
       <c r="H5" t="n">
-        <v>703.4400000000001</v>
+        <v>717.6799999999999</v>
       </c>
       <c r="I5" t="n">
         <v>713.5441687210439</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.88</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="M5" t="n">
         <v>0.9</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H6" t="n">
-        <v>684.35</v>
+        <v>675.72</v>
       </c>
       <c r="I6" t="n">
         <v>679.4566174793462</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.64</v>
+        <v>-5.85</v>
       </c>
       <c r="L6" t="n">
-        <v>5.22</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
         <v>0.6899999999999999</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42310</v>
+        <v>42311</v>
       </c>
       <c r="H7" t="n">
-        <v>650.48</v>
+        <v>687.41</v>
       </c>
       <c r="I7" t="n">
         <v>672.3423735925821</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>3.74</v>
+        <v>-1.73</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>3.56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.05</v>
+        <v>4.22</v>
       </c>
       <c r="N7" t="n">
-        <v>3.92</v>
+        <v>5.68</v>
       </c>
       <c r="O7" t="n">
         <v>-1.26</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H8" t="n">
-        <v>674.1900000000001</v>
+        <v>642.86</v>
       </c>
       <c r="I8" t="n">
         <v>659.1942073184367</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.92</v>
+        <v>-6.48</v>
       </c>
       <c r="L8" t="n">
-        <v>3.06</v>
+        <v>7.69</v>
       </c>
       <c r="M8" t="n">
         <v>2.72</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.52</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42424</v>
+        <v>42425</v>
       </c>
       <c r="H9" t="n">
-        <v>518.47</v>
+        <v>533.12</v>
       </c>
       <c r="I9" t="n">
         <v>531.9268677731228</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
-        <v>19.35</v>
+        <v>17.07</v>
       </c>
       <c r="L9" t="n">
         <v>7.3</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>15.44</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42438</v>
+        <v>42439</v>
       </c>
       <c r="H10" t="n">
-        <v>482.82</v>
+        <v>469.8</v>
       </c>
       <c r="I10" t="n">
         <v>472.3949718584055</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.44</v>
+        <v>-11.88</v>
       </c>
       <c r="L10" t="n">
-        <v>10.71</v>
+        <v>13.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.44</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H11" t="n">
-        <v>497.89</v>
+        <v>519.15</v>
       </c>
       <c r="I11" t="n">
         <v>510.2895442256442</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.98</v>
+        <v>-10.5</v>
       </c>
       <c r="L11" t="n">
         <v>12.81</v>
@@ -1068,7 +1199,7 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>4.27</v>
       </c>
       <c r="O11" t="n">
         <v>-2.7</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.77</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42508</v>
+        <v>42509</v>
       </c>
       <c r="H12" t="n">
-        <v>506.87</v>
+        <v>489.03</v>
       </c>
       <c r="I12" t="n">
         <v>489.0398849596926</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.37</v>
+        <v>-5.8</v>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>6.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.84</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42551</v>
+        <v>42552</v>
       </c>
       <c r="H13" t="n">
-        <v>500.03</v>
+        <v>513.73</v>
       </c>
       <c r="I13" t="n">
         <v>505.6686987581237</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.25</v>
+        <v>-5.05</v>
       </c>
       <c r="L13" t="n">
-        <v>4.87</v>
+        <v>5.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.17</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
         <v>-3.52</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42565</v>
+        <v>42566</v>
       </c>
       <c r="H14" t="n">
-        <v>499.92</v>
+        <v>489.23</v>
       </c>
       <c r="I14" t="n">
         <v>491.81571797616</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.69</v>
+        <v>-4.77</v>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>5.85</v>
       </c>
       <c r="M14" t="n">
         <v>0.53</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
         <v>2.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42642</v>
+        <v>42643</v>
       </c>
       <c r="H15" t="n">
-        <v>461.12</v>
+        <v>493.29</v>
       </c>
       <c r="I15" t="n">
         <v>482.4201368030028</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K15" t="n">
-        <v>5.75</v>
+        <v>-0.83</v>
       </c>
       <c r="L15" t="n">
         <v>6.25</v>
@@ -1296,7 +1475,7 @@
         <v>2.31</v>
       </c>
       <c r="N15" t="n">
-        <v>4.32</v>
+        <v>6.98</v>
       </c>
       <c r="O15" t="n">
         <v>-2.14</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>11.48</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H16" t="n">
-        <v>465.67</v>
+        <v>454.35</v>
       </c>
       <c r="I16" t="n">
         <v>460.6044752597929</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.6</v>
+        <v>-7.89</v>
       </c>
       <c r="L16" t="n">
-        <v>5.92</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>2.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
         <v>6.98</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42751</v>
+        <v>42752</v>
       </c>
       <c r="H17" t="n">
-        <v>391.46</v>
+        <v>417.03</v>
       </c>
       <c r="I17" t="n">
         <v>394.9926349725613</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
-        <v>13.84</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>3.15</v>
@@ -1410,7 +1613,7 @@
         <v>1.85</v>
       </c>
       <c r="N17" t="n">
-        <v>5.23</v>
+        <v>6.53</v>
       </c>
       <c r="O17" t="n">
         <v>-2.43</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.01</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42810</v>
+        <v>42811</v>
       </c>
       <c r="H18" t="n">
-        <v>443.49</v>
+        <v>441.11</v>
       </c>
       <c r="I18" t="n">
         <v>441.2058367011908</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K18" t="n">
-        <v>6.34</v>
+        <v>5.77</v>
       </c>
       <c r="L18" t="n">
         <v>6.43</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42865</v>
+        <v>42866</v>
       </c>
       <c r="H19" t="n">
-        <v>392.52</v>
+        <v>427.25</v>
       </c>
       <c r="I19" t="n">
         <v>406.4208235181474</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" t="n">
-        <v>11.02</v>
+        <v>3.14</v>
       </c>
       <c r="L19" t="n">
         <v>1.51</v>
@@ -1524,7 +1751,7 @@
         <v>1.16</v>
       </c>
       <c r="N19" t="n">
-        <v>3.46</v>
+        <v>8.85</v>
       </c>
       <c r="O19" t="n">
         <v>-0.54</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>12.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H20" t="n">
-        <v>409.04</v>
+        <v>384.16</v>
       </c>
       <c r="I20" t="n">
         <v>391.2340364261466</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.26</v>
+        <v>-10.09</v>
       </c>
       <c r="L20" t="n">
-        <v>7.78</v>
+        <v>10.51</v>
       </c>
       <c r="M20" t="n">
         <v>1.32</v>
       </c>
       <c r="N20" t="n">
-        <v>3.58</v>
+        <v>6.08</v>
       </c>
       <c r="O20" t="n">
         <v>8.85</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>16.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42885</v>
+        <v>42886</v>
       </c>
       <c r="H21" t="n">
-        <v>418.49</v>
+        <v>453.07</v>
       </c>
       <c r="I21" t="n">
         <v>447.5528067008053</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.94</v>
+        <v>-17.94</v>
       </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>21.15</v>
       </c>
       <c r="M21" t="n">
-        <v>1.21</v>
+        <v>3.71</v>
       </c>
       <c r="N21" t="n">
-        <v>7.32</v>
+        <v>8.26</v>
       </c>
       <c r="O21" t="n">
         <v>-6.08</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>14.66</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H22" t="n">
-        <v>507.19</v>
+        <v>498.16</v>
       </c>
       <c r="I22" t="n">
         <v>501.8174470671768</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K22" t="n">
-        <v>11.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>4.61</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H23" t="n">
-        <v>507.74</v>
+        <v>514.9299999999999</v>
       </c>
       <c r="I23" t="n">
         <v>508.6140227277335</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.92</v>
+        <v>-3.37</v>
       </c>
       <c r="L23" t="n">
         <v>9.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.75</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H24" t="n">
-        <v>750.12</v>
+        <v>697.5700000000001</v>
       </c>
       <c r="I24" t="n">
         <v>724.3657693068442</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>45.67</v>
+        <v>35.47</v>
       </c>
       <c r="L24" t="n">
         <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>0.95</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.74</v>
+        <v>7.01</v>
       </c>
       <c r="O24" t="n">
         <v>1.42</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H25" t="n">
-        <v>665.53</v>
+        <v>670.03</v>
       </c>
       <c r="I25" t="n">
         <v>667.2766716905101</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K25" t="n">
-        <v>4.59</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
         <v>4.01</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.66</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43228</v>
+        <v>43229</v>
       </c>
       <c r="H26" t="n">
-        <v>671.99</v>
+        <v>659.55</v>
       </c>
       <c r="I26" t="n">
         <v>669.6959558851036</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K26" t="n">
-        <v>0.29</v>
+        <v>-1.56</v>
       </c>
       <c r="L26" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
         <v>0.55</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H27" t="n">
-        <v>675.59</v>
+        <v>685.61</v>
       </c>
       <c r="I27" t="n">
         <v>679.5834771595745</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.43</v>
+        <v>-3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>4.13</v>
+        <v>4.47</v>
       </c>
       <c r="M27" t="n">
         <v>2.56</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.81</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43285</v>
+        <v>43286</v>
       </c>
       <c r="H28" t="n">
-        <v>666.9</v>
+        <v>629.25</v>
       </c>
       <c r="I28" t="n">
         <v>638.3754197548765</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.73</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>7.91</v>
+        <v>8.84</v>
       </c>
       <c r="M28" t="n">
         <v>0.92</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>5.65</v>
       </c>
       <c r="O28" t="n">
         <v>1.48</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.47</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43328</v>
+        <v>43329</v>
       </c>
       <c r="H29" t="n">
-        <v>627.35</v>
+        <v>638.65</v>
       </c>
       <c r="I29" t="n">
         <v>631.5876884610412</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3</v>
+        <v>-1.49</v>
       </c>
       <c r="L29" t="n">
         <v>5.52</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>10.34</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H30" t="n">
-        <v>602.6</v>
+        <v>594.15</v>
       </c>
       <c r="I30" t="n">
         <v>595.4751291826462</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.64</v>
+        <v>-6.97</v>
       </c>
       <c r="L30" t="n">
-        <v>7.11</v>
+        <v>8.85</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="N30" t="n">
         <v>3.27</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43385</v>
+        <v>43388</v>
       </c>
       <c r="H31" t="n">
-        <v>521.7</v>
+        <v>533.2</v>
       </c>
       <c r="I31" t="n">
         <v>524.5374243909328</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>12.19</v>
+        <v>10.26</v>
       </c>
       <c r="L31" t="n">
         <v>2.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43468</v>
+        <v>43469</v>
       </c>
       <c r="H32" t="n">
-        <v>620.1</v>
+        <v>604.6</v>
       </c>
       <c r="I32" t="n">
         <v>605.3895144337196</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K32" t="n">
-        <v>16.3</v>
+        <v>13.39</v>
       </c>
       <c r="L32" t="n">
         <v>6.4</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.91</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H33" t="n">
-        <v>546.25</v>
+        <v>564.6</v>
       </c>
       <c r="I33" t="n">
         <v>562.0065357143264</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K33" t="n">
-        <v>9.65</v>
+        <v>6.62</v>
       </c>
       <c r="L33" t="n">
         <v>2.55</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>11.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43551</v>
+        <v>43552</v>
       </c>
       <c r="H34" t="n">
-        <v>539.95</v>
+        <v>532.4</v>
       </c>
       <c r="I34" t="n">
         <v>537.6398780805763</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.37</v>
+        <v>-5.7</v>
       </c>
       <c r="L34" t="n">
-        <v>4.89</v>
+        <v>6.08</v>
       </c>
       <c r="M34" t="n">
         <v>0.68</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43619</v>
+        <v>43620</v>
       </c>
       <c r="H35" t="n">
-        <v>557.6</v>
+        <v>571.8</v>
       </c>
       <c r="I35" t="n">
         <v>562.9314417422402</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.73</v>
+        <v>-7.4</v>
       </c>
       <c r="L35" t="n">
-        <v>6.11</v>
+        <v>7.96</v>
       </c>
       <c r="M35" t="n">
         <v>2.02</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.86</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43747</v>
+        <v>43748</v>
       </c>
       <c r="H36" t="n">
-        <v>621.5</v>
+        <v>615.15</v>
       </c>
       <c r="I36" t="n">
         <v>615.8344718700744</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K36" t="n">
-        <v>8.69</v>
+        <v>7.58</v>
       </c>
       <c r="L36" t="n">
         <v>10.59</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.12</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43857</v>
+        <v>43858</v>
       </c>
       <c r="H37" t="n">
-        <v>575.7</v>
+        <v>655.9</v>
       </c>
       <c r="I37" t="n">
         <v>604.561568650695</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K37" t="n">
-        <v>6.41</v>
+        <v>-6.62</v>
       </c>
       <c r="L37" t="n">
-        <v>5.66</v>
+        <v>7.83</v>
       </c>
       <c r="M37" t="n">
-        <v>1.49</v>
+        <v>4.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>13.93</v>
       </c>
       <c r="O37" t="n">
         <v>-1.02</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.92</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H38" t="n">
-        <v>686.35</v>
+        <v>657.45</v>
       </c>
       <c r="I38" t="n">
         <v>661.854493121498</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K38" t="n">
-        <v>4.64</v>
+        <v>0.24</v>
       </c>
       <c r="L38" t="n">
         <v>9.59</v>
@@ -2607,7 +3062,7 @@
         <v>0.93</v>
       </c>
       <c r="N38" t="n">
-        <v>3.22</v>
+        <v>4.21</v>
       </c>
       <c r="O38" t="n">
         <v>13.93</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.07</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43970</v>
+        <v>43971</v>
       </c>
       <c r="H39" t="n">
-        <v>555.1</v>
+        <v>575.15</v>
       </c>
       <c r="I39" t="n">
         <v>572.3703080354984</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K39" t="n">
-        <v>15.57</v>
+        <v>12.52</v>
       </c>
       <c r="L39" t="n">
         <v>6.89</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44069</v>
+        <v>44070</v>
       </c>
       <c r="H40" t="n">
-        <v>574.95</v>
+        <v>570.1</v>
       </c>
       <c r="I40" t="n">
         <v>572.2652956931034</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.03</v>
+        <v>-0.88</v>
       </c>
       <c r="L40" t="n">
         <v>3.16</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H41" t="n">
-        <v>533.95</v>
+        <v>544.2</v>
       </c>
       <c r="I41" t="n">
         <v>540.1379150998433</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K41" t="n">
-        <v>6.34</v>
+        <v>4.54</v>
       </c>
       <c r="L41" t="n">
         <v>3.82</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.95</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H42" t="n">
-        <v>644.9</v>
+        <v>594.4</v>
       </c>
       <c r="I42" t="n">
         <v>599.0141976198536</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K42" t="n">
-        <v>18.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>1.98</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>7.83</v>
       </c>
       <c r="O42" t="n">
         <v>1.92</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>14.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44327</v>
+        <v>44328</v>
       </c>
       <c r="H43" t="n">
-        <v>555.05</v>
+        <v>559.4</v>
       </c>
       <c r="I43" t="n">
         <v>556.463662201593</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K43" t="n">
-        <v>6.62</v>
+        <v>5.89</v>
       </c>
       <c r="L43" t="n">
         <v>5.79</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H44" t="n">
-        <v>833.9</v>
+        <v>826.3</v>
       </c>
       <c r="I44" t="n">
         <v>828.7765735825108</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K44" t="n">
-        <v>49.07</v>
+        <v>47.71</v>
       </c>
       <c r="L44" t="n">
         <v>1.4</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H45" t="n">
-        <v>892.55</v>
+        <v>947.35</v>
       </c>
       <c r="I45" t="n">
         <v>904.4794695517722</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.02</v>
+        <v>-14.65</v>
       </c>
       <c r="L45" t="n">
-        <v>14.33</v>
+        <v>16.59</v>
       </c>
       <c r="M45" t="n">
         <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.81</v>
+        <v>6.14</v>
       </c>
       <c r="O45" t="n">
         <v>-0.91</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>14.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H46" t="n">
-        <v>942.35</v>
+        <v>885.7</v>
       </c>
       <c r="I46" t="n">
         <v>900.22333578158</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.53</v>
+        <v>-6.51</v>
       </c>
       <c r="L46" t="n">
-        <v>6.95</v>
+        <v>6.97</v>
       </c>
       <c r="M46" t="n">
-        <v>0.38</v>
+        <v>1.31</v>
       </c>
       <c r="N46" t="n">
-        <v>3.38</v>
+        <v>6.01</v>
       </c>
       <c r="O46" t="n">
         <v>6.14</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H47" t="n">
-        <v>914.7</v>
+        <v>942.35</v>
       </c>
       <c r="I47" t="n">
         <v>942.2402177304054</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.27</v>
+        <v>-6.4</v>
       </c>
       <c r="L47" t="n">
-        <v>6.01</v>
+        <v>7.33</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H48" t="n">
-        <v>899.3</v>
+        <v>855.35</v>
       </c>
       <c r="I48" t="n">
         <v>876.8480923319281</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.57</v>
+        <v>-9.23</v>
       </c>
       <c r="L48" t="n">
-        <v>5.54</v>
+        <v>10.16</v>
       </c>
       <c r="M48" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="N48" t="n">
-        <v>3.06</v>
+        <v>4.89</v>
       </c>
       <c r="O48" t="n">
         <v>3.02</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.29</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H49" t="n">
-        <v>858.25</v>
+        <v>877.25</v>
       </c>
       <c r="I49" t="n">
         <v>874.9876731427502</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.34</v>
+        <v>-2.56</v>
       </c>
       <c r="L49" t="n">
         <v>5.14</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.93</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H50" t="n">
-        <v>886.9</v>
+        <v>859</v>
       </c>
       <c r="I50" t="n">
         <v>859.7556077687864</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K50" t="n">
-        <v>1.1</v>
+        <v>-2.08</v>
       </c>
       <c r="L50" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="M50" t="n">
         <v>0.89</v>
       </c>
       <c r="N50" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O50" t="n">
         <v>2.21</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.66</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H51" t="n">
-        <v>793.05</v>
+        <v>809.7</v>
       </c>
       <c r="I51" t="n">
         <v>808.9572741672388</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K51" t="n">
-        <v>7.68</v>
+        <v>5.74</v>
       </c>
       <c r="L51" t="n">
         <v>5.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.25</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44768</v>
+        <v>44769</v>
       </c>
       <c r="H52" t="n">
-        <v>850.35</v>
+        <v>792.9</v>
       </c>
       <c r="I52" t="n">
         <v>796.670143663321</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>5.02</v>
+        <v>-2.07</v>
       </c>
       <c r="L52" t="n">
-        <v>2.19</v>
+        <v>3.04</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5</v>
+        <v>1.81</v>
       </c>
       <c r="N52" t="n">
-        <v>1.72</v>
+        <v>6.76</v>
       </c>
       <c r="O52" t="n">
         <v>2.1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>11.66</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44813</v>
+        <v>44816</v>
       </c>
       <c r="H53" t="n">
-        <v>808.15</v>
+        <v>838.4</v>
       </c>
       <c r="I53" t="n">
         <v>828.0128473911532</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.92</v>
+        <v>-5.74</v>
       </c>
       <c r="L53" t="n">
-        <v>5.61</v>
+        <v>6.27</v>
       </c>
       <c r="M53" t="n">
         <v>1.49</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.4</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H54" t="n">
-        <v>898.05</v>
+        <v>874.25</v>
       </c>
       <c r="I54" t="n">
         <v>888.4145183366737</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K54" t="n">
-        <v>7.11</v>
+        <v>4.28</v>
       </c>
       <c r="L54" t="n">
         <v>4.34</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H55" t="n">
-        <v>779.2</v>
+        <v>785.85</v>
       </c>
       <c r="I55" t="n">
         <v>782.0959492350183</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K55" t="n">
-        <v>10.87</v>
+        <v>10.11</v>
       </c>
       <c r="L55" t="n">
         <v>2.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.74</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45198</v>
+        <v>45202</v>
       </c>
       <c r="H56" t="n">
-        <v>1007.25</v>
+        <v>998.75</v>
       </c>
       <c r="I56" t="n">
         <v>1000.533444329266</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K56" t="n">
-        <v>28.17</v>
+        <v>27.09</v>
       </c>
       <c r="L56" t="n">
         <v>1.85</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.52</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45210</v>
+        <v>45211</v>
       </c>
       <c r="H57" t="n">
-        <v>1050.35</v>
+        <v>1053.25</v>
       </c>
       <c r="I57" t="n">
         <v>1051.495893069952</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.17</v>
+        <v>-5.46</v>
       </c>
       <c r="L57" t="n">
-        <v>5.53</v>
+        <v>6.36</v>
       </c>
       <c r="M57" t="n">
         <v>1.16</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.12</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H58" t="n">
-        <v>1040.1</v>
+        <v>1012.1</v>
       </c>
       <c r="I58" t="n">
         <v>1019.289135850847</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.25</v>
+        <v>-3.91</v>
       </c>
       <c r="L58" t="n">
-        <v>2.33</v>
+        <v>4.32</v>
       </c>
       <c r="M58" t="n">
         <v>1.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.25</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H59" t="n">
-        <v>1070.35</v>
+        <v>1082.7</v>
       </c>
       <c r="I59" t="n">
         <v>1076.74080262929</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.76</v>
+        <v>-6.98</v>
       </c>
       <c r="L59" t="n">
-        <v>6.96</v>
+        <v>7.2</v>
       </c>
       <c r="M59" t="n">
         <v>1.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.68</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H60" t="n">
-        <v>1108.3</v>
+        <v>1087.45</v>
       </c>
       <c r="I60" t="n">
         <v>1091.100311382579</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K60" t="n">
-        <v>2.36</v>
+        <v>0.44</v>
       </c>
       <c r="L60" t="n">
         <v>5.43</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.75</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H61" t="n">
-        <v>1128.35</v>
+        <v>1200.1</v>
       </c>
       <c r="I61" t="n">
         <v>1178.156125385666</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.76</v>
+        <v>-10.36</v>
       </c>
       <c r="L61" t="n">
-        <v>7.59</v>
+        <v>10.76</v>
       </c>
       <c r="M61" t="n">
         <v>0.92</v>
       </c>
       <c r="N61" t="n">
-        <v>2.22</v>
+        <v>6.36</v>
       </c>
       <c r="O61" t="n">
         <v>-1.88</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.71</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H62" t="n">
-        <v>1531.35</v>
+        <v>1506.3</v>
       </c>
       <c r="I62" t="n">
         <v>1516.292889051368</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K62" t="n">
-        <v>27.6</v>
+        <v>25.51</v>
       </c>
       <c r="L62" t="n">
         <v>6.82</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>7</v>
+      </c>
+      <c r="U62" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H63" t="n">
-        <v>1532.2</v>
+        <v>1542.95</v>
       </c>
       <c r="I63" t="n">
         <v>1533.12180854973</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.72</v>
+        <v>-2.43</v>
       </c>
       <c r="L63" t="n">
         <v>3.63</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.79</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H64" t="n">
-        <v>1574.45</v>
+        <v>1539.15</v>
       </c>
       <c r="I64" t="n">
         <v>1561.025232420875</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K64" t="n">
-        <v>2.04</v>
+        <v>-0.25</v>
       </c>
       <c r="L64" t="n">
         <v>4.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.04</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45742</v>
+        <v>45743</v>
       </c>
       <c r="H65" t="n">
-        <v>1361.5</v>
+        <v>1408.1</v>
       </c>
       <c r="I65" t="n">
         <v>1406.163689188332</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K65" t="n">
-        <v>11.54</v>
+        <v>8.51</v>
       </c>
       <c r="L65" t="n">
         <v>2.98</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.65</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H66" t="n">
-        <v>1503.8</v>
+        <v>1485.1</v>
       </c>
       <c r="I66" t="n">
         <v>1501.044362448034</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K66" t="n">
-        <v>6.8</v>
+        <v>5.47</v>
       </c>
       <c r="L66" t="n">
         <v>3.13</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>10.58</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="H67" t="n">
-        <v>1346.7</v>
+        <v>1362.6</v>
       </c>
       <c r="I67" t="n">
         <v>1359.413923179229</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K67" t="n">
-        <v>9.32</v>
+        <v>8.25</v>
       </c>
       <c r="L67" t="n">
         <v>1.97</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H68" t="n">
-        <v>1377.8</v>
+        <v>1350.2</v>
       </c>
       <c r="I68" t="n">
         <v>1374.78015951364</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K68" t="n">
-        <v>1.12</v>
+        <v>-0.91</v>
       </c>
       <c r="L68" t="n">
         <v>4.59</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.27</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H69" t="n">
-        <v>1377</v>
+        <v>1409.8</v>
       </c>
       <c r="I69" t="n">
         <v>1390.83178768942</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.98</v>
+        <v>-4.41</v>
       </c>
       <c r="L69" t="n">
-        <v>2.13</v>
+        <v>4.68</v>
       </c>
       <c r="M69" t="n">
         <v>1.37</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>7.8</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H70" t="n">
-        <v>1366.6</v>
+        <v>1316.8</v>
       </c>
       <c r="I70" t="n">
         <v>1350.567032917718</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.06</v>
+        <v>-6.6</v>
       </c>
       <c r="L70" t="n">
-        <v>4.6</v>
+        <v>6.99</v>
       </c>
       <c r="M70" t="n">
         <v>2.59</v>
       </c>
       <c r="N70" t="n">
-        <v>1.93</v>
+        <v>3.64</v>
       </c>
       <c r="O70" t="n">
         <v>2.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.26</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H71" t="n">
-        <v>1307.7</v>
+        <v>1363</v>
       </c>
       <c r="I71" t="n">
         <v>1351.493000570692</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K71" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.51</v>
       </c>
       <c r="L71" t="n">
         <v>7.68</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>10.22</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H72" t="n">
-        <v>1315.6</v>
+        <v>1290.3</v>
       </c>
       <c r="I72" t="n">
         <v>1290.552284629076</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.48</v>
+        <v>-5.33</v>
       </c>
       <c r="L72" t="n">
-        <v>4.08</v>
+        <v>6.87</v>
       </c>
       <c r="M72" t="n">
         <v>0.98</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,25 +5456,25 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H73" t="n">
-        <v>1308</v>
+        <v>1350.3</v>
       </c>
       <c r="I73" t="n">
         <v>1322.174502238481</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.37</v>
+        <v>-4.65</v>
       </c>
       <c r="L73" t="n">
-        <v>4.01</v>
+        <v>5.99</v>
       </c>
       <c r="M73" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="N73" t="n">
         <v>3.79</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.85</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H74" t="n">
-        <v>1470</v>
+        <v>1469.5</v>
       </c>
       <c r="I74" t="n">
         <v>1469.726648056017</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K74" t="n">
-        <v>8.859999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="L74" t="n">
         <v>2.84</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>38</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107.8</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="11">
@@ -9737,7 +10644,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -9747,7 +10654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -9757,7 +10664,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.9</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="14">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.84</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.42</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.22</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.07</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.1</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.29</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.9</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.33</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="25">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.88</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="27">
@@ -9897,7 +10804,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.27</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="28">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
